--- a/v2/tests/fixtures/casos_legacy/REGLAS.xlsx
+++ b/v2/tests/fixtures/casos_legacy/REGLAS.xlsx
@@ -2521,7 +2521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,6 +2568,35 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Comentario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B2" t="n">
+        <v>168617</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OPERADOR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DOCUFO 10.25 07/24/2024 144A: reestructuración, valor acordado con PM</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2789,6 +2818,38 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>politica_hedge</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>XCCY_SI_EXISTE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hedgeados: XCCY_SI_EXISTE (swap de mercado, si no drop propio) o DROP_SIEMPRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>xccy_drop_max_bps</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Alerta XCCY_VS_DROP cuando |XCCY − drop propio| supera estos bps</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/v2/tests/fixtures/casos_legacy/REGLAS.xlsx
+++ b/v2/tests/fixtures/casos_legacy/REGLAS.xlsx
@@ -2667,7 +2667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2724,6 +2724,704 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>Descripcion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YIELD_ALTA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>param:yield_alta_default</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CRITICA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yield final sobre el umbral general</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>YIELD_ALTA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>param:yield_alta_local</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CRITICA</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>MLDL: monedas locales, umbral más alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>YIELD_NEGATIVA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yield final negativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DEFAULT_CON_AI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Default_Con_AI</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>es_verdadero</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Default con devengo positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BONO_SIN_AI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bono_Sin_AI</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>es_verdadero</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bono no default con AI = 0 (¿cupón cero, recién pagó o default no marcado?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PRECIO_Y_YIELD_SUBEN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Precio_Sube_Yield_Sube</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>es_verdadero</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CRITICA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Precio y yield suben a la vez vs cierre anterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>METRICAS_SIN_ACTUALIZAR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Metricas_Iguales_Ant</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>es_verdadero</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yield y duration idénticas al cierre anterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DELTA_YIELD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Delta_Yield</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>abs&gt;=</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>param:delta_yield_max</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Cambio de yield vs cierre anterior sobre el umbral</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COBERTURA_BAJA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cobertura_MV_Fondo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>param:cobertura_min_mv</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FONDO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>MV de activos con métrica bajo el mínimo del fondo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FALTANTE_CON_MV</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Falta_Con_MV</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>es_verdadero</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Duplicaría la estructural FALTANTE; se deja como ejemplo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HEDGE_CONVERTIDO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>XCCY;DROP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Ejemplo de operador in (desactivada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SIN_TRATAMIENTO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tratamiento</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>igual</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SIN_REGLA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ejemplo: en Excel '==' se vuelve fórmula, se escribe igual</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PROVEEDOR_INVALIDO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ajuste de estructural: baja de ALTA a MEDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>YIELD_TYPE_DEFAULT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ajuste de estructural: silenciada</t>
         </is>
       </c>
     </row>
@@ -2738,7 +3436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2850,6 +3548,66 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>yield_alta_default</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A01: yield final sobre este valor es CRÍTICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>yield_alta_local</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A01 en fondos de moneda local (MLDL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>delta_yield_max</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A07: |Δ yield| vs cierre anterior (10 pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cobertura_min_mv</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A09: cobertura mínima de MV de activos con métrica por fondo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
